--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119630194</v>
+        <v>119630193</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577553</v>
+        <v>577549</v>
       </c>
       <c r="R33" t="n">
-        <v>6628426</v>
+        <v>6628425</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ca 150 bladrosetter bland blåbärsris intill björk</t>
+          <t>Ca 55 bladrosetter bland blåbärsris under gran. En stjälk öveblommad och fortfarande grön.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4978,7 +4978,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119630197</v>
+        <v>119630196</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577543</v>
+        <v>577548</v>
       </c>
       <c r="R34" t="n">
         <v>6628426</v>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ca 75 bladrosetter och 11 helt bruna stjälkar, i mossa med blåbär, vid basen av tall med orange ledmarkering,  på stigens norra sida. Inom någon meter från stigen.</t>
+          <t>Ca 40 bladrosetter och 3 bruna stjälkar. Söder om stigen på mossklätt mindre stenblock.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5104,7 +5104,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119630193</v>
+        <v>119630197</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5152,18 +5152,16 @@
           <t>frukt-/fröspridning</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577549</v>
+        <v>577543</v>
       </c>
       <c r="R35" t="n">
-        <v>6628425</v>
+        <v>6628426</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5200,7 +5198,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ca 55 bladrosetter bland blåbärsris under gran. En stjälk öveblommad och fortfarande grön.</t>
+          <t>Ca 75 bladrosetter och 11 helt bruna stjälkar, i mossa med blåbär, vid basen av tall med orange ledmarkering,  på stigens norra sida. Inom någon meter från stigen.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5209,7 +5207,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5233,7 +5230,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119630196</v>
+        <v>119630194</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -5268,7 +5265,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5281,13 +5278,15 @@
           <t>frukt-/fröspridning</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577548</v>
+        <v>577553</v>
       </c>
       <c r="R36" t="n">
         <v>6628426</v>
@@ -5327,7 +5326,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ca 40 bladrosetter och 3 bruna stjälkar. Söder om stigen på mossklätt mindre stenblock.</t>
+          <t>Ca 150 bladrosetter bland blåbärsris intill björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5336,6 +5335,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4720,7 +4720,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119622307</v>
+        <v>119630196</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4763,22 +4763,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svanå bruk (knärot), Vstm</t>
+          <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577551</v>
+        <v>577548</v>
       </c>
       <c r="R32" t="n">
         <v>6628426</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4800,11 +4802,6 @@
           <t>Haraker</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>U-Väs-1374</t>
-        </is>
-      </c>
       <c r="Y32" t="inlineStr">
         <is>
           <t>2024-09-08</t>
@@ -4817,7 +4814,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ca 320 bladrosetter. Inlagda som fyra privata fynd i Artportalen med bilder. Ett av fynden norr om stigen och tre av fynden söder om stigen. Justerade centrumkoordinaten, då 2022 års fynd var angivet vid koordinaten O1532340, N6629765  (±10m), där vi inte såg någon knärot idag.</t>
+          <t>Ca 40 bladrosetter och 3 bruna stjälkar. Söder om stigen på mossklätt mindre stenblock.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4826,9 +4823,13 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4841,11 +4842,7 @@
           <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4978,7 +4975,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119630196</v>
+        <v>119630194</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -5013,7 +5010,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5026,13 +5023,15 @@
           <t>frukt-/fröspridning</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577548</v>
+        <v>577553</v>
       </c>
       <c r="R34" t="n">
         <v>6628426</v>
@@ -5072,7 +5071,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ca 40 bladrosetter och 3 bruna stjälkar. Söder om stigen på mossklätt mindre stenblock.</t>
+          <t>Ca 150 bladrosetter bland blåbärsris intill björk</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5081,6 +5080,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5104,7 +5104,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119630197</v>
+        <v>119622307</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>320</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5147,24 +5147,22 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svanå bruk, Vstm</t>
+          <t>Svanå bruk (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577543</v>
+        <v>577551</v>
       </c>
       <c r="R35" t="n">
         <v>6628426</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5186,6 +5184,11 @@
           <t>Haraker</t>
         </is>
       </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>U-Väs-1374</t>
+        </is>
+      </c>
       <c r="Y35" t="inlineStr">
         <is>
           <t>2024-09-08</t>
@@ -5198,7 +5201,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ca 75 bladrosetter och 11 helt bruna stjälkar, i mossa med blåbär, vid basen av tall med orange ledmarkering,  på stigens norra sida. Inom någon meter från stigen.</t>
+          <t>Ca 320 bladrosetter. Inlagda som fyra privata fynd i Artportalen med bilder. Ett av fynden norr om stigen och tre av fynden söder om stigen. Justerade centrumkoordinaten, då 2022 års fynd var angivet vid koordinaten O1532340, N6629765  (±10m), där vi inte såg någon knärot idag.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5207,13 +5210,9 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5226,11 +5225,15 @@
           <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119630194</v>
+        <v>119630197</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -5265,7 +5268,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5278,15 +5281,13 @@
           <t>frukt-/fröspridning</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577553</v>
+        <v>577543</v>
       </c>
       <c r="R36" t="n">
         <v>6628426</v>
@@ -5326,7 +5327,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ca 150 bladrosetter bland blåbärsris intill björk</t>
+          <t>Ca 75 bladrosetter och 11 helt bruna stjälkar, i mossa med blåbär, vid basen av tall med orange ledmarkering,  på stigens norra sida. Inom någon meter från stigen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5335,7 +5336,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4846,7 +4846,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119630193</v>
+        <v>119622307</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>320</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4889,26 +4889,22 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svanå bruk, Vstm</t>
+          <t>Svanå bruk (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577549</v>
+        <v>577551</v>
       </c>
       <c r="R33" t="n">
-        <v>6628425</v>
+        <v>6628426</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4930,6 +4926,11 @@
           <t>Haraker</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>U-Väs-1374</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
           <t>2024-09-08</t>
@@ -4942,7 +4943,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ca 55 bladrosetter bland blåbärsris under gran. En stjälk öveblommad och fortfarande grön.</t>
+          <t>Ca 320 bladrosetter. Inlagda som fyra privata fynd i Artportalen med bilder. Ett av fynden norr om stigen och tre av fynden söder om stigen. Justerade centrumkoordinaten, då 2022 års fynd var angivet vid koordinaten O1532340, N6629765  (±10m), där vi inte såg någon knärot idag.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4955,11 +4956,6 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
@@ -4971,7 +4967,11 @@
           <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5104,7 +5104,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119622307</v>
+        <v>119630193</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5147,22 +5147,26 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svanå bruk (knärot), Vstm</t>
+          <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577551</v>
+        <v>577549</v>
       </c>
       <c r="R35" t="n">
-        <v>6628426</v>
+        <v>6628425</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5184,11 +5188,6 @@
           <t>Haraker</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>U-Väs-1374</t>
-        </is>
-      </c>
       <c r="Y35" t="inlineStr">
         <is>
           <t>2024-09-08</t>
@@ -5201,7 +5200,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ca 320 bladrosetter. Inlagda som fyra privata fynd i Artportalen med bilder. Ett av fynden norr om stigen och tre av fynden söder om stigen. Justerade centrumkoordinaten, då 2022 års fynd var angivet vid koordinaten O1532340, N6629765  (±10m), där vi inte såg någon knärot idag.</t>
+          <t>Ca 55 bladrosetter bland blåbärsris under gran. En stjälk öveblommad och fortfarande grön.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5214,6 +5213,11 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -5225,11 +5229,7 @@
           <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>98081</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4889,7 +4889,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,12 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4968,7 +4963,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
+          <t>Bengt Stridh, Josefin Kjellberg, Dennis JP Nyström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Josefin Kjellberg, Dennis JP Nyström</t>
+          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
+          <t>Bengt Stridh, Josefin Kjellberg, Dennis JP Nyström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -4849,7 +4849,7 @@
         <v>119622307</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4963043</v>
+        <v>98450567</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577574.7263844567</v>
+        <v>577510</v>
       </c>
       <c r="R2" t="n">
-        <v>6628248.65238499</v>
+        <v>6628606</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-07-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-07-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,73 +768,90 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>forsmiljö</t>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Einar Marklund, Tom Sävström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16865276</v>
+        <v>98450560</v>
       </c>
       <c r="B3" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>241</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svanå bruk, Övre dammen, O, Vstm</t>
+          <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577578.0991792245</v>
+        <v>577523</v>
       </c>
       <c r="R3" t="n">
-        <v>6628280.449229009</v>
+        <v>6628569</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,27 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-11-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-11-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,87 +889,95 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>gammal granskog</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov, uppsågad granlåga</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16865281</v>
+        <v>98450563</v>
       </c>
       <c r="B4" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>241</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svanå bruk, Övre dammen, O, Vstm</t>
+          <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577478.6856478223</v>
+        <v>577489</v>
       </c>
       <c r="R4" t="n">
-        <v>6628597.139037832</v>
+        <v>6628761</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,27 +1001,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-11-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-11-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sparsam förekomst.</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,95 +1015,95 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>blandskogsbryn</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>2</v>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova granstubbar</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16865377</v>
+        <v>98450568</v>
       </c>
       <c r="B5" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>241</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svanå bruk, Övre dammen; O, Vstm</t>
+          <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577489.7359217592</v>
+        <v>577510</v>
       </c>
       <c r="R5" t="n">
-        <v>6628599.383350318</v>
+        <v>6628606</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,27 +1127,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-11-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-11-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Klibbticka på samma granlåga.</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,73 +1141,82 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>äldre, fuktig granskog nära åstrand</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov rotvälta av gran</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16911049</v>
+        <v>17210323</v>
       </c>
       <c r="B6" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1241,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577597.1555124955</v>
+        <v>577586</v>
       </c>
       <c r="R6" t="n">
-        <v>6628310.054864773</v>
+        <v>6628511</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1271,27 +1254,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-11-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-11-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Täml. riklig förekomst.</t>
+          <t>2015-03-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1306,7 +1274,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>gammal granskog</t>
+          <t>äldre granskog</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1314,7 +1282,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov, stående död gran</t>
+          <t>1 substratenheter # nästan barklös granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1332,44 +1300,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17036062</v>
+        <v>57641451</v>
       </c>
       <c r="B7" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1378,14 +1337,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svanå bruk, Övre dammen, O, Vstm</t>
+          <t>Övre dammen (SÖ), Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577513.3987316496</v>
+        <v>577494</v>
       </c>
       <c r="R7" t="n">
-        <v>6628528.874966795</v>
+        <v>6628642</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1412,22 +1371,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-01-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-01-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1440,91 +1389,102 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>granskogsbryn</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
+          <t>Äldre granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # granstubbe</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17036063</v>
+        <v>98450561</v>
       </c>
       <c r="B8" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svanå bruk, Övre dammen, O, Vstm</t>
+          <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577500.4916649031</v>
+        <v>577504</v>
       </c>
       <c r="R8" t="n">
-        <v>6628591.550549431</v>
+        <v>6628605</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1548,22 +1508,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-01-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-01-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,47 +1522,48 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>fuktig blandskog</t>
-        </is>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # stående död gran</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17210323</v>
+        <v>98450566</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1639,28 +1590,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svanå bruk, Övre dammen, O, Vstm</t>
+          <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577586.4128787589</v>
+        <v>577467</v>
       </c>
       <c r="R9" t="n">
-        <v>6628510.757777236</v>
+        <v>6628678</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1684,22 +1634,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-03-19</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-03-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1708,95 +1648,86 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>äldre granskog</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # nästan barklös granlåga</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>54860878</v>
+        <v>98450571</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svanå bruk, Övre dammen, O, Vstm</t>
+          <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577536.4187385694</v>
+        <v>577613</v>
       </c>
       <c r="R10" t="n">
-        <v>6628368.211956345</v>
+        <v>6628308</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1820,22 +1751,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-08-16</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-08-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1844,83 +1765,86 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>äldre granskog</t>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>57641443</v>
+        <v>98450572</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övre dammen (SÖ), Vstm</t>
+          <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577584.2071595528</v>
+        <v>577601</v>
       </c>
       <c r="R11" t="n">
-        <v>6628519.775903621</v>
+        <v>6628311</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1944,22 +1868,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-03-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2016-03-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1968,18 +1882,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre granskog</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1992,88 +1900,68 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Grov, barklös granlåga # Picea abies</t>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>57640812</v>
+        <v>98450573</v>
       </c>
       <c r="B12" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1445</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Övre dammen (SÖ), Vstm</t>
+          <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577579.8112678517</v>
+        <v>577601</v>
       </c>
       <c r="R12" t="n">
-        <v>6628270.916629624</v>
+        <v>6628311</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2097,22 +1985,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2016-03-17</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2016-03-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2121,71 +1999,75 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre granskog på moränmark</t>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>På granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>57640681</v>
+        <v>16865377</v>
       </c>
       <c r="B13" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2196,14 +2078,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Övre dammen (SÖ), Vstm</t>
+          <t>Svanå bruk, Övre dammen; O, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577585.2314316217</v>
+        <v>577490</v>
       </c>
       <c r="R13" t="n">
-        <v>6628252.900166961</v>
+        <v>6628599</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2230,27 +2112,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2016-03-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2016-03-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ny fyndplats!</t>
+          <t>Klibbticka på samma granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2263,44 +2135,42 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre granskog på moränmark</t>
+          <t>äldre, fuktig granskog nära åstrand</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov rotvälta av gran</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>57641251</v>
+        <v>57640681</v>
       </c>
       <c r="B14" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2323,7 +2193,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2338,10 +2208,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577535.0529050699</v>
+        <v>577585</v>
       </c>
       <c r="R14" t="n">
-        <v>6628361.1333494</v>
+        <v>6628253</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2371,19 +2241,14 @@
           <t>2016-03-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2016-03-17</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ny fyndplats!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2403,7 +2268,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre granskog på moränmark, intill vandringsled</t>
+          <t>Äldre granskog på moränmark</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2421,19 +2286,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>57640958</v>
+        <v>57640812</v>
       </c>
       <c r="B15" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2471,10 +2331,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577579.0966266841</v>
+        <v>577580</v>
       </c>
       <c r="R15" t="n">
-        <v>6628256.801046623</v>
+        <v>6628271</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2504,19 +2364,9 @@
           <t>2016-03-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2016-03-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2536,7 +2386,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre granskog på moränmark, intill vandringsled</t>
+          <t>Äldre granskog på moränmark</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2554,19 +2404,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>57641123</v>
+        <v>57640958</v>
       </c>
       <c r="B16" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2589,7 +2434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2604,10 +2449,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577526.1455321343</v>
+        <v>577579</v>
       </c>
       <c r="R16" t="n">
-        <v>6628377.062370272</v>
+        <v>6628257</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2637,19 +2482,9 @@
           <t>2016-03-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2016-03-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2687,40 +2522,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>57641451</v>
+        <v>57641123</v>
       </c>
       <c r="B17" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1445</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -2733,10 +2567,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577493.8972731109</v>
+        <v>577526</v>
       </c>
       <c r="R17" t="n">
-        <v>6628641.767984953</v>
+        <v>6628377</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2766,19 +2600,9 @@
           <t>2016-03-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2016-03-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2798,27 +2622,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Äldre granskog på moränmark, intill vandringsled</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2836,37 +2640,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>57617966</v>
+        <v>57641251</v>
       </c>
       <c r="B18" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1445</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2874,26 +2673,25 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svanå bruk, Övre dammen, O, Vstm</t>
+          <t>Övre dammen (SÖ), Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577565.7184288669</v>
+        <v>577535</v>
       </c>
       <c r="R18" t="n">
-        <v>6628462.991154138</v>
+        <v>6628361</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2920,103 +2718,90 @@
           <t>2016-03-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2016-03-17</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre granskog på moränmark, intill vandringsled</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95301337</v>
+        <v>16865276</v>
       </c>
       <c r="B19" t="n">
-        <v>56387</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100004</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfiskare</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alcedo atthis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svanå 30, Västerås, Vstm</t>
+          <t>Svanå bruk, Övre dammen, O, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577508.0145477627</v>
+        <v>577578</v>
       </c>
       <c r="R19" t="n">
-        <v>6628375.677518812</v>
+        <v>6628280</v>
       </c>
       <c r="S19" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3040,22 +2825,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3064,33 +2844,42 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>gammal granskog</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov, uppsågad granlåga</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Jonsson</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Jonsson</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>98450567</v>
+        <v>16865281</v>
       </c>
       <c r="B20" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3098,46 +2887,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svanå bruk, Vstm</t>
+          <t>Svanå bruk, Övre dammen, O, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577509.2735422228</v>
+        <v>577479</v>
       </c>
       <c r="R20" t="n">
-        <v>6628605.832880666</v>
+        <v>6628597</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3161,22 +2943,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Sparsam förekomst.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3185,91 +2962,82 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
+          <t>blandskogsbryn</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>2</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>2 substratenheter # grova granstubbar</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>98450572</v>
+        <v>16911049</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svanå bruk, Vstm</t>
+          <t>Svanå bruk, Övre dammen, O, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577600.6641290587</v>
+        <v>577597</v>
       </c>
       <c r="R21" t="n">
-        <v>6628311.135208443</v>
+        <v>6628310</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3293,22 +3061,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-11-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Täml. riklig förekomst.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3317,91 +3080,90 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
+          <t>gammal granskog</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>1 substratenheter # grov, stående död gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>98450573</v>
+        <v>17036062</v>
       </c>
       <c r="B22" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svanå bruk, Vstm</t>
+          <t>Svanå bruk, Övre dammen, O, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577600.6641290587</v>
+        <v>577513</v>
       </c>
       <c r="R22" t="n">
-        <v>6628311.135208443</v>
+        <v>6628529</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3425,22 +3187,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-01-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-01-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3449,100 +3201,90 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
+          <t>granskogsbryn</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>1 substratenheter # granstubbe</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>98450560</v>
+        <v>17036063</v>
       </c>
       <c r="B23" t="n">
-        <v>83354</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svanå bruk, Vstm</t>
+          <t>Svanå bruk, Övre dammen, O, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577522.6542943236</v>
+        <v>577500</v>
       </c>
       <c r="R23" t="n">
-        <v>6628568.848795705</v>
+        <v>6628592</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3566,22 +3308,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-01-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-01-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3590,53 +3322,42 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
+          <t>fuktig blandskog</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>1 substratenheter # stående död gran</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>98450562</v>
+        <v>98450564</v>
       </c>
       <c r="B24" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3644,21 +3365,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>4189</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3668,7 +3389,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3677,10 +3398,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577464.3449470379</v>
+        <v>577466</v>
       </c>
       <c r="R24" t="n">
-        <v>6628752.937778942</v>
+        <v>6628742</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3710,19 +3431,14 @@
           <t>2021-12-23</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-12-23</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>I barrmatta under äldre gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3737,6 +3453,11 @@
       <c r="AI24" t="inlineStr">
         <is>
           <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Barrmatta</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3754,37 +3475,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>98450564</v>
+        <v>54860878</v>
       </c>
       <c r="B25" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4189</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3797,19 +3513,20 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svanå bruk, Vstm</t>
+          <t>Svanå bruk, Övre dammen, O, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577465.5733464211</v>
+        <v>577536</v>
       </c>
       <c r="R25" t="n">
-        <v>6628742.389225196</v>
+        <v>6628368</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3833,27 +3550,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I barrmatta under äldre gran</t>
+          <t>2015-08-16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3862,81 +3564,78 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Barrmatta</t>
+          <t>äldre granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>98450571</v>
+        <v>57641443</v>
       </c>
       <c r="B26" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svanå bruk, Vstm</t>
+          <t>Övre dammen (SÖ), Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577612.8391363901</v>
+        <v>577584</v>
       </c>
       <c r="R26" t="n">
-        <v>6628307.863986737</v>
+        <v>6628520</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3960,22 +3659,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3984,12 +3673,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4002,35 +3697,35 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>På granlåga # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Grov, barklös granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>98450566</v>
+        <v>95301199</v>
       </c>
       <c r="B27" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57937</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4038,21 +3733,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100004</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfiskare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alcedo atthis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4060,24 +3755,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svanå bruk, Vstm</t>
+          <t>Svanå 30, Västerås, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577466.4104906486</v>
+        <v>577508</v>
       </c>
       <c r="R27" t="n">
-        <v>6628677.954173042</v>
+        <v>6628376</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4101,22 +3798,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4127,73 +3814,48 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>På granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Johan Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Johan Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>98450568</v>
+        <v>57617966</v>
       </c>
       <c r="B28" t="n">
-        <v>83354</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>241</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4201,24 +3863,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svanå bruk, Vstm</t>
+          <t>Svanå bruk, Övre dammen, O, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577509.2735422228</v>
+        <v>577566</v>
       </c>
       <c r="R28" t="n">
-        <v>6628605.832880666</v>
+        <v>6628463</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4242,22 +3906,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-03-17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4268,95 +3922,77 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>På granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>98450561</v>
+        <v>98838461</v>
       </c>
       <c r="B29" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577504.2316432819</v>
+        <v>577522</v>
       </c>
       <c r="R29" t="n">
-        <v>6628605.727856995</v>
+        <v>6628411</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4383,22 +4019,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4407,27 +4033,13 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>På granlåga # Picea abies</t>
+          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4438,69 +4050,69 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Jacob Rudhe, Henrik Berg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>98450563</v>
+        <v>104436674</v>
       </c>
       <c r="B30" t="n">
-        <v>83354</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>241</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svanå bruk, Vstm</t>
+          <t>Svanå bruk (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577488.377387381</v>
+        <v>577551</v>
       </c>
       <c r="R30" t="n">
-        <v>6628761.494669928</v>
+        <v>6628426</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4522,24 +4134,19 @@
           <t>Haraker</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>U-Väs-1374</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4553,48 +4160,32 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>På granlåga # Picea abies</t>
+          <t>äldre granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Jacob Rudhe, Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>98838461</v>
+        <v>119630193</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4621,17 +4212,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4642,10 +4233,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577521.9133990555</v>
+        <v>577549</v>
       </c>
       <c r="R31" t="n">
-        <v>6628410.713927428</v>
+        <v>6628425</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4672,22 +4263,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 55 bladrosetter bland blåbärsris under gran. En stjälk öveblommad och fortfarande grön.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4702,33 +4288,28 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Äldre granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Bengt Stridh</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Henrik Berg</t>
+          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119630196</v>
+        <v>119630194</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4755,7 +4336,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4768,13 +4349,15 @@
           <t>frukt-/fröspridning</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577548</v>
+        <v>577553</v>
       </c>
       <c r="R32" t="n">
         <v>6628426</v>
@@ -4814,7 +4397,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ca 40 bladrosetter och 3 bruna stjälkar. Söder om stigen på mossklätt mindre stenblock.</t>
+          <t>Ca 150 bladrosetter bland blåbärsris intill björk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4823,6 +4406,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4846,10 +4430,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119622307</v>
+        <v>119630196</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4876,7 +4460,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4889,21 +4473,19 @@
           <t>frukt-/fröspridning</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svanå bruk (knärot), Vstm</t>
+          <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577551</v>
+        <v>577548</v>
       </c>
       <c r="R33" t="n">
         <v>6628426</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4925,11 +4507,6 @@
           <t>Haraker</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>U-Väs-1374</t>
-        </is>
-      </c>
       <c r="Y33" t="inlineStr">
         <is>
           <t>2024-09-08</t>
@@ -4942,7 +4519,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ca 320 bladrosetter. Inlagda som fyra privata fynd i Artportalen med bilder. Ett av fynden norr om stigen och tre av fynden söder om stigen. Justerade centrumkoordinaten, då 2022 års fynd var angivet vid koordinaten O1532340, N6629765  (±10m), där vi inte såg någon knärot idag.</t>
+          <t>Ca 40 bladrosetter och 3 bruna stjälkar. Söder om stigen på mossklätt mindre stenblock.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4951,9 +4528,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4966,23 +4547,14 @@
           <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119630194</v>
+        <v>119630197</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5009,7 +4581,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5022,15 +4594,13 @@
           <t>frukt-/fröspridning</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577553</v>
+        <v>577543</v>
       </c>
       <c r="R34" t="n">
         <v>6628426</v>
@@ -5070,7 +4640,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ca 150 bladrosetter bland blåbärsris intill björk</t>
+          <t>Ca 75 bladrosetter och 11 helt bruna stjälkar, i mossa med blåbär, vid basen av tall med orange ledmarkering,  på stigens norra sida. Inom någon meter från stigen.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5079,7 +4649,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5103,66 +4672,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119630193</v>
+        <v>98450562</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577549</v>
+        <v>577465</v>
       </c>
       <c r="R35" t="n">
-        <v>6628425</v>
+        <v>6628753</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5189,17 +4746,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ca 55 bladrosetter bland blåbärsris under gran. En stjälk öveblommad och fortfarande grön.</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5208,91 +4760,71 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119630197</v>
+        <v>4963043</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svanå bruk, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577543</v>
+        <v>577575</v>
       </c>
       <c r="R36" t="n">
-        <v>6628426</v>
+        <v>6628249</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5316,17 +4848,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2012-07-31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ca 75 bladrosetter och 11 helt bruna stjälkar, i mossa med blåbär, vid basen av tall med orange ledmarkering,  på stigens norra sida. Inom någon meter från stigen.</t>
+          <t>2012-07-31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5340,18 +4867,18 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>forsmiljö</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
+          <t>Einar Marklund, Tom Sävström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 67268-2021 artfynd.xlsx
+++ b/artfynd/A 67268-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450567</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450560</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450563</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450568</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210323</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1431,6 +1461,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57641451</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1557,6 +1592,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450561</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1683,6 +1723,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450566</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1800,6 +1845,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450571</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1917,6 +1967,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450572</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2034,6 +2089,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450573</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2160,6 +2220,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16865377</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2283,6 +2348,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57640681</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2401,6 +2471,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57640812</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2519,6 +2594,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57640958</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2637,6 +2717,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57641123</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2755,6 +2840,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57641251</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2873,6 +2963,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16865276</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2991,6 +3086,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16865281</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3109,6 +3209,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16911049</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3230,6 +3335,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17036062</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3351,6 +3461,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17036063</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3472,6 +3587,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450564</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3585,6 +3705,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54860878</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3719,6 +3844,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57641443</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3827,6 +3957,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95301199</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3935,6 +4070,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57617966</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4054,6 +4194,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98838461</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4179,6 +4324,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104436674</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4303,6 +4453,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119630193</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4427,6 +4582,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119630194</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4548,6 +4708,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119630196</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4669,6 +4834,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119630197</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4780,6 +4950,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98450562</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4882,8 +5057,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4963043</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>